--- a/testsheets/TestSuite.xlsx
+++ b/testsheets/TestSuite.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\keyword_pw_python_framework\testsheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\keyword_excel_framework\testsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BB3C5F7-D1BA-4D68-BA3F-9E681B4C8480}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{217EE310-D8E5-46B7-94A1-22C24BF9ACFA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7425" tabRatio="811" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/testsheets/TestSuite.xlsx
+++ b/testsheets/TestSuite.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\keyword_excel_framework\testsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{217EE310-D8E5-46B7-94A1-22C24BF9ACFA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B93DE9-5FB2-4227-B03C-BD7B94BDD3C6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7425" tabRatio="811" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="252">
   <si>
     <t>TestCase ID</t>
   </si>
@@ -785,6 +785,9 @@
   </si>
   <si>
     <t>INTENTIONAL FAIL - demonstrates VerifyJsonSchema actually catches a broken contract, not just passes silently</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200 OK </t>
   </si>
 </sst>
 </file>
@@ -3780,7 +3783,7 @@
         <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>121</v>
+        <v>251</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>13</v>

--- a/testsheets/TestSuite.xlsx
+++ b/testsheets/TestSuite.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\keyword_excel_framework\testsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B93DE9-5FB2-4227-B03C-BD7B94BDD3C6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AE1A297-0171-4DB0-9927-1587DBE4D7F7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7425" tabRatio="811" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7425" tabRatio="811" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TestSteps" sheetId="1" r:id="rId1"/>
@@ -1210,7 +1210,7 @@
         <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>22</v>

--- a/testsheets/TestSuite.xlsx
+++ b/testsheets/TestSuite.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\keyword_excel_framework\testsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AE1A297-0171-4DB0-9927-1587DBE4D7F7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66732137-901D-4536-BDB1-D06B3C223983}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7425" tabRatio="811" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7425" tabRatio="811" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TestSteps" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="252">
   <si>
     <t>TestCase ID</t>
   </si>
@@ -1210,7 +1210,7 @@
         <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>22</v>
@@ -2229,7 +2229,7 @@
         <v>89</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
@@ -2367,8 +2367,8 @@
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
-      <c r="G7" s="1" t="s">
-        <v>112</v>
+      <c r="G7" s="1">
+        <v>404</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>113</v>
